--- a/batch_example.xlsx
+++ b/batch_example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cillian_dendra2\dendra2_AnalysisCode\PubliclyShared_GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB55A98-490C-42A7-9C78-A2C949D915FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13D72E7-DD53-4A84-BF70-F2D5F7D9D243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23295" yWindow="1245" windowWidth="14400" windowHeight="10545" xr2:uid="{7C5C9096-F65B-4F75-888F-184F04F3F8EF}"/>
   </bookViews>
@@ -44,13 +44,13 @@
     <t>DirectoryNames</t>
   </si>
   <si>
-    <t>C:\Desktop\dendra2\Experiment1</t>
+    <t>C:\dendra2\Experiment1</t>
   </si>
   <si>
-    <t>C:\Desktop\dendra2\Experiment3</t>
+    <t>C:\dendra2\Experiment2</t>
   </si>
   <si>
-    <t>C:\Desktop\dendra2\Experiment2</t>
+    <t>C:\dendra2\Experiment3</t>
   </si>
 </sst>
 </file>
@@ -451,12 +451,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
